--- a/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17T02:00:37.393929+00:00</t>
+          <t>2026-08-28T13:31:58.420547+00:00</t>
         </is>
       </c>
     </row>

--- a/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28T13:31:58.420547+00:00</t>
+          <t>2026-08-28T18:49:53.220713+00:00</t>
         </is>
       </c>
     </row>

--- a/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28T18:49:53.220713+00:00</t>
+          <t>2026-08-28T20:13:47.903954+00:00</t>
         </is>
       </c>
     </row>

--- a/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28T20:13:47.903954+00:00</t>
+          <t>2026-08-31T23:48:51.976270+00:00</t>
         </is>
       </c>
     </row>

--- a/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31T23:48:51.976270+00:00</t>
+          <t>2026-09-01T00:10:26.191025+00:00</t>
         </is>
       </c>
     </row>

--- a/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01T00:10:26.191025+00:00</t>
+          <t>2026-09-01T00:38:12.797681+00:00</t>
         </is>
       </c>
     </row>

--- a/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/5_Artist_Platform_Performance.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01T00:38:12.797681+00:00</t>
+          <t>2026-09-01T01:12:21.685661+00:00</t>
         </is>
       </c>
     </row>
